--- a/src/test/resources/testdata/ExpenseSheets.xlsx
+++ b/src/test/resources/testdata/ExpenseSheets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationScripts\Auto\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationScripts\TripGain_TestCases\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7A91BD-33D6-4761-9900-5A950750B29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9457E204-9EE7-484A-B1A4-847B08D787CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{C7B9F131-33C4-4D68-AE47-F0F4C988FB80}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{C7B9F131-33C4-4D68-AE47-F0F4C988FB80}"/>
   </bookViews>
   <sheets>
     <sheet name="TCE_1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="TCE_5" sheetId="6" r:id="rId4"/>
     <sheet name="TCE_6" sheetId="7" r:id="rId5"/>
     <sheet name="TCE_2" sheetId="2" r:id="rId6"/>
+    <sheet name="TCE_7" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
   <si>
     <t>TestRun</t>
   </si>
@@ -74,13 +75,85 @@
   </si>
   <si>
     <t>Done</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Origin</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>TripName</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>PASTRIP_1</t>
+  </si>
+  <si>
+    <t>https://neo.tripgain.com/login</t>
+  </si>
+  <si>
+    <t>testtraveller98@tripgain.com</t>
+  </si>
+  <si>
+    <t>@AM@TGA1$29TN</t>
+  </si>
+  <si>
+    <t>Dubai</t>
+  </si>
+  <si>
+    <t>UserName1</t>
+  </si>
+  <si>
+    <t>Password1</t>
+  </si>
+  <si>
+    <t>SearchBy</t>
+  </si>
+  <si>
+    <t>SearchValue</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>automation@tga.com</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>testapprover98@tripgain.com</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>TravellerSearchValue</t>
+  </si>
+  <si>
+    <t>TravellerSearchValue2</t>
+  </si>
+  <si>
+    <t>testfinanceadmin98@tripgain.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +173,26 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667085"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -118,15 +211,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -657,4 +761,113 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3019DBBD-7D81-4536-B2D9-36D7724F65DC}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.1796875" customWidth="1"/>
+    <col min="2" max="2" width="26.36328125" customWidth="1"/>
+    <col min="3" max="3" width="18.08984375" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" customWidth="1"/>
+    <col min="5" max="5" width="12.90625" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="18.36328125" customWidth="1"/>
+    <col min="12" max="12" width="17.90625" customWidth="1"/>
+    <col min="13" max="13" width="19.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{A4191AE8-8F42-454D-8967-32E5C11ABA40}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>